--- a/data/processed_data/Video_491_EXP5_CTRL1_36HZ/serie_temporal.xlsx
+++ b/data/processed_data/Video_491_EXP5_CTRL1_36HZ/serie_temporal.xlsx
@@ -697,7 +697,7 @@
         <v>0.09666666666666669</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>255.5566772659289</v>
+        <v>255.5566772659288</v>
       </c>
     </row>
     <row r="6">
@@ -79860,7 +79860,7 @@
         <v>62.16333333333333</v>
       </c>
       <c r="M1846" s="2" t="n">
-        <v>255.8464562778374</v>
+        <v>255.8464562778376</v>
       </c>
     </row>
     <row r="1847">
@@ -79903,7 +79903,7 @@
         <v>62.2</v>
       </c>
       <c r="M1847" s="2" t="n">
-        <v>255.8178063700187</v>
+        <v>255.8178063700189</v>
       </c>
     </row>
   </sheetData>
@@ -79918,7 +79918,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -80319,6 +80319,36 @@
         <v>0.9459</v>
       </c>
     </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>error de modelo borde sup (px)</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n">
+        <v>1.2718</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>error de modelo borde inf (px)</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>1.0028</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>error de modelo peor / grosor (%)</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="n">
+        <v>0.498</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
